--- a/حسابداری/بانک ها/رسالت ابوالفضل/1405/14050101-14050131.xlsx
+++ b/حسابداری/بانک ها/رسالت ابوالفضل/1405/14050101-14050131.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\بانک ها\رسالت ابوالفضل\1405\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\حسابداری باکسینو\حسابداری\بانک ها\رسالت ابوالفضل\1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBA57CC9-8309-453F-80BB-14C75E6F85CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D220993A-2946-4605-8841-C1CF1D067AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Table1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Table1!$A$3:$O$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Table1!$A$3:$O$17</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="60">
   <si>
     <t>صورت حساب سپرده</t>
   </si>
@@ -188,13 +188,28 @@
   </si>
   <si>
     <t>پرداخت کارمزد</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1404/12/27</t>
+  </si>
+  <si>
+    <t>12:55:07</t>
+  </si>
+  <si>
+    <t>کارمزد ارسال پیامک دی 1404_برداشت بابت فایل (GW-1773838277401)</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="9"/>
       <name val="Tahoma"/>
@@ -225,8 +240,15 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -296,6 +318,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor rgb="FFCCCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor rgb="FFCCCCCC"/>
       </patternFill>
     </fill>
@@ -327,7 +361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -383,6 +417,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -704,7 +756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -793,187 +845,181 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="2">
+    <row r="4" spans="1:15" s="19" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" s="24">
+        <v>109770</v>
+      </c>
+      <c r="G4" s="24">
+        <v>0</v>
+      </c>
+      <c r="H4" s="24">
+        <v>63421128</v>
+      </c>
+      <c r="I4" s="20"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="21"/>
+    </row>
+    <row r="5" spans="1:15" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="12" t="s">
+      <c r="B5" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D5" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F5" s="13">
         <v>9000</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G5" s="13">
         <v>0</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H5" s="13">
         <v>63412128</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="6">
-        <v>9</v>
-      </c>
-      <c r="O4" s="6">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="1">
-        <v>2</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="15">
-        <v>5000000</v>
-      </c>
-      <c r="G5" s="15">
-        <v>0</v>
-      </c>
-      <c r="H5" s="15">
-        <v>58412128</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="6">
-        <v>10</v>
-      </c>
+      <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
-      <c r="M5" s="6">
+      <c r="M5" s="5"/>
+      <c r="N5" s="6">
+        <v>9</v>
+      </c>
+      <c r="O5" s="6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="15">
+        <v>5000000</v>
+      </c>
+      <c r="G6" s="15">
+        <v>0</v>
+      </c>
+      <c r="H6" s="15">
+        <v>58412128</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="6">
+        <v>10</v>
+      </c>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="6">
         <v>93</v>
       </c>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-    </row>
-    <row r="6" spans="1:15" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="2">
-        <v>3</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="13">
-        <v>0</v>
-      </c>
-      <c r="G6" s="16">
-        <v>1470000</v>
-      </c>
-      <c r="H6" s="13">
-        <v>59882128</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="9">
-        <v>11</v>
-      </c>
-      <c r="M6" s="5"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
     </row>
     <row r="7" spans="1:15" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="1">
-        <v>4</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="15">
-        <v>100000</v>
-      </c>
-      <c r="G7" s="15">
+      <c r="A7" s="2">
+        <v>3</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="13">
         <v>0</v>
       </c>
-      <c r="H7" s="15">
-        <v>59782128</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="6">
-        <v>11</v>
-      </c>
+      <c r="G7" s="16">
+        <v>1470000</v>
+      </c>
+      <c r="H7" s="13">
+        <v>59882128</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" s="5"/>
       <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="6">
-        <v>91</v>
-      </c>
+      <c r="L7" s="9">
+        <v>11</v>
+      </c>
+      <c r="M7" s="5"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
     </row>
     <row r="8" spans="1:15" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="2">
-        <v>5</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="13">
-        <v>2195000</v>
-      </c>
-      <c r="G8" s="13">
+      <c r="A8" s="1">
+        <v>4</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="15">
+        <v>100000</v>
+      </c>
+      <c r="G8" s="15">
         <v>0</v>
       </c>
-      <c r="H8" s="13">
-        <v>57587128</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>43</v>
+      <c r="H8" s="15">
+        <v>59782128</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="J8" s="6">
         <v>11</v>
@@ -987,297 +1033,336 @@
       <c r="O8" s="5"/>
     </row>
     <row r="9" spans="1:15" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="1">
-        <v>6</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="14" t="s">
+      <c r="A9" s="2">
+        <v>5</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="15">
-        <v>1788012</v>
-      </c>
-      <c r="G9" s="15">
+      <c r="D9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="13">
+        <v>2195000</v>
+      </c>
+      <c r="G9" s="13">
         <v>0</v>
       </c>
-      <c r="H9" s="15">
-        <v>55799116</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>44</v>
+      <c r="H9" s="13">
+        <v>57587128</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="J9" s="6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="6">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
     </row>
     <row r="10" spans="1:15" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="2">
-        <v>7</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="12" t="s">
+      <c r="A10" s="1">
+        <v>6</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="13">
-        <v>9000</v>
-      </c>
-      <c r="G10" s="13">
+      <c r="D10" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="15">
+        <v>1788012</v>
+      </c>
+      <c r="G10" s="15">
         <v>0</v>
       </c>
-      <c r="H10" s="13">
-        <v>55790116</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J10" s="5"/>
+      <c r="H10" s="15">
+        <v>55799116</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" s="6">
+        <v>12</v>
+      </c>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="6">
-        <v>9</v>
-      </c>
-      <c r="O10" s="6">
-        <v>90</v>
-      </c>
+      <c r="M10" s="6">
+        <v>92</v>
+      </c>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
     </row>
     <row r="11" spans="1:15" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="1">
-        <v>8</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="14" t="s">
+      <c r="A11" s="2">
+        <v>7</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="15">
-        <v>3500000</v>
-      </c>
-      <c r="G11" s="15">
+      <c r="E11" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="13">
+        <v>9000</v>
+      </c>
+      <c r="G11" s="13">
         <v>0</v>
       </c>
-      <c r="H11" s="15">
-        <v>52290116</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="J11" s="6">
-        <v>13</v>
-      </c>
+      <c r="H11" s="13">
+        <v>55790116</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="J11" s="5"/>
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
-      <c r="M11" s="6">
-        <v>94</v>
-      </c>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="6">
+        <v>9</v>
+      </c>
+      <c r="O11" s="6">
+        <v>90</v>
+      </c>
     </row>
     <row r="12" spans="1:15" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="2">
-        <v>9</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="13">
-        <v>1430000</v>
-      </c>
-      <c r="G12" s="13">
+      <c r="A12" s="1">
+        <v>8</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="15">
+        <v>3500000</v>
+      </c>
+      <c r="G12" s="15">
         <v>0</v>
       </c>
-      <c r="H12" s="13">
-        <v>50860116</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>48</v>
+      <c r="H12" s="15">
+        <v>52290116</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="J12" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
       <c r="M12" s="6">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
     </row>
     <row r="13" spans="1:15" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="1">
-        <v>10</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="15">
-        <v>9000</v>
-      </c>
-      <c r="G13" s="15">
+      <c r="A13" s="2">
+        <v>9</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="13">
+        <v>1430000</v>
+      </c>
+      <c r="G13" s="13">
         <v>0</v>
       </c>
-      <c r="H13" s="15">
-        <v>50851116</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="J13" s="5"/>
+      <c r="H13" s="13">
+        <v>50860116</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="J13" s="6">
+        <v>11</v>
+      </c>
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="6">
-        <v>9</v>
-      </c>
-      <c r="O13" s="6">
-        <v>90</v>
-      </c>
+      <c r="M13" s="6">
+        <v>91</v>
+      </c>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
     </row>
     <row r="14" spans="1:15" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="2">
-        <v>11</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="12" t="s">
+      <c r="A14" s="1">
+        <v>10</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="13">
-        <v>2000000</v>
-      </c>
-      <c r="G14" s="13">
+      <c r="E14" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="15">
+        <v>9000</v>
+      </c>
+      <c r="G14" s="15">
         <v>0</v>
       </c>
-      <c r="H14" s="13">
-        <v>48851116</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="J14" s="6">
-        <v>10</v>
-      </c>
+      <c r="H14" s="15">
+        <v>50851116</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J14" s="5"/>
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
-      <c r="M14" s="6">
-        <v>93</v>
-      </c>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="6">
+        <v>9</v>
+      </c>
+      <c r="O14" s="6">
+        <v>90</v>
+      </c>
     </row>
     <row r="15" spans="1:15" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="1">
-        <v>12</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F15" s="15">
-        <v>300000</v>
-      </c>
-      <c r="G15" s="15">
+      <c r="A15" s="2">
+        <v>11</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="13">
+        <v>2000000</v>
+      </c>
+      <c r="G15" s="13">
         <v>0</v>
       </c>
-      <c r="H15" s="15">
-        <v>48551116</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>46</v>
+      <c r="H15" s="13">
+        <v>48851116</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="J15" s="6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
       <c r="M15" s="6">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
     </row>
     <row r="16" spans="1:15" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="1">
+        <v>12</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="15">
+        <v>300000</v>
+      </c>
+      <c r="G16" s="15">
+        <v>0</v>
+      </c>
+      <c r="H16" s="15">
+        <v>48551116</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" s="6">
+        <v>11</v>
+      </c>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="6">
+        <v>91</v>
+      </c>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+    </row>
+    <row r="17" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:O16" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:O17" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A17:I17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
